--- a/junction_leakiness_mix_1.0_ws_200_zero_weight_0.4_leak_thresh_0.1_fl_0_a_1.0_1.xlsx
+++ b/junction_leakiness_mix_1.0_ws_200_zero_weight_0.4_leak_thresh_0.1_fl_0_a_1.0_1.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/amit/BIO/FINAL/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44E07B0-89DD-5046-A33F-E12F322C6FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="21140" windowHeight="16120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -112,8 +118,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,13 +182,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -220,7 +234,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -254,6 +268,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -288,9 +303,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -463,11 +479,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE231"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,7 +575,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -567,10 +583,10 @@
         <v>12911</v>
       </c>
       <c r="C2">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="D2">
-        <v>19.81</v>
+        <v>19.809999999999999</v>
       </c>
       <c r="E2">
         <v>22.35</v>
@@ -612,10 +628,10 @@
         <v>12911</v>
       </c>
       <c r="R2">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="S2">
-        <v>19.81</v>
+        <v>19.809999999999999</v>
       </c>
       <c r="T2">
         <v>22.35</v>
@@ -654,7 +670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -665,10 +681,10 @@
         <v>9.02</v>
       </c>
       <c r="D3">
-        <v>40.45</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="E3">
-        <v>39.41</v>
+        <v>39.409999999999997</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -710,10 +726,10 @@
         <v>9.02</v>
       </c>
       <c r="S3">
-        <v>40.45</v>
+        <v>40.450000000000003</v>
       </c>
       <c r="T3">
-        <v>39.41</v>
+        <v>39.409999999999997</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -749,7 +765,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -763,7 +779,7 @@
         <v>45.32</v>
       </c>
       <c r="E4">
-        <v>75.68000000000001</v>
+        <v>75.680000000000007</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -808,7 +824,7 @@
         <v>45.32</v>
       </c>
       <c r="T4">
-        <v>75.68000000000001</v>
+        <v>75.680000000000007</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -844,7 +860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -852,7 +868,7 @@
         <v>10999</v>
       </c>
       <c r="C5">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="D5">
         <v>20.58</v>
@@ -897,7 +913,7 @@
         <v>10999</v>
       </c>
       <c r="R5">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="S5">
         <v>20.58</v>
@@ -939,7 +955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1034,7 +1050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1045,7 +1061,7 @@
         <v>1.7</v>
       </c>
       <c r="D7">
-        <v>40.12</v>
+        <v>40.119999999999997</v>
       </c>
       <c r="E7">
         <v>57.21</v>
@@ -1090,7 +1106,7 @@
         <v>1.7</v>
       </c>
       <c r="S7">
-        <v>40.12</v>
+        <v>40.119999999999997</v>
       </c>
       <c r="T7">
         <v>57.21</v>
@@ -1129,7 +1145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1152,7 +1168,7 @@
         <v>0.72</v>
       </c>
       <c r="H8">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1164,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>72.04000000000001</v>
+        <v>72.040000000000006</v>
       </c>
       <c r="M8">
         <v>1000.19</v>
@@ -1197,7 +1213,7 @@
         <v>0.72</v>
       </c>
       <c r="W8">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="X8">
         <v>0</v>
@@ -1209,7 +1225,7 @@
         <v>0.01</v>
       </c>
       <c r="AA8">
-        <v>72.04000000000001</v>
+        <v>72.040000000000006</v>
       </c>
       <c r="AB8">
         <v>1000.19</v>
@@ -1224,7 +1240,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1232,7 +1248,7 @@
         <v>35913</v>
       </c>
       <c r="C9">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="D9">
         <v>41.89</v>
@@ -1247,7 +1263,7 @@
         <v>0.93</v>
       </c>
       <c r="H9">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1277,7 +1293,7 @@
         <v>35913</v>
       </c>
       <c r="R9">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="S9">
         <v>41.89</v>
@@ -1292,7 +1308,7 @@
         <v>0.93</v>
       </c>
       <c r="W9">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X9">
         <v>0</v>
@@ -1319,7 +1335,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1333,7 +1349,7 @@
         <v>53.47</v>
       </c>
       <c r="E10">
-        <v>78.90000000000001</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1354,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>534.1900000000001</v>
+        <v>534.19000000000005</v>
       </c>
       <c r="M10">
         <v>151.78</v>
@@ -1378,7 +1394,7 @@
         <v>53.47</v>
       </c>
       <c r="T10">
-        <v>78.90000000000001</v>
+        <v>78.900000000000006</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1399,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>534.1900000000001</v>
+        <v>534.19000000000005</v>
       </c>
       <c r="AB10">
         <v>151.78</v>
@@ -1414,7 +1430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1434,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H11">
         <v>0.06</v>
@@ -1479,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="V11">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W11">
         <v>0.06</v>
@@ -1509,7 +1525,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1517,7 +1533,7 @@
         <v>29926</v>
       </c>
       <c r="C12">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="D12">
         <v>35.6</v>
@@ -1562,7 +1578,7 @@
         <v>29926</v>
       </c>
       <c r="R12">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="S12">
         <v>35.6</v>
@@ -1604,7 +1620,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1612,7 +1628,7 @@
         <v>7471</v>
       </c>
       <c r="C13">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="D13">
         <v>27.16</v>
@@ -1657,7 +1673,7 @@
         <v>7471</v>
       </c>
       <c r="R13">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="S13">
         <v>27.16</v>
@@ -1699,7 +1715,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1794,7 +1810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1808,7 +1824,7 @@
         <v>59.8</v>
       </c>
       <c r="E15">
-        <v>81.43000000000001</v>
+        <v>81.430000000000007</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -1853,7 +1869,7 @@
         <v>59.8</v>
       </c>
       <c r="T15">
-        <v>81.43000000000001</v>
+        <v>81.430000000000007</v>
       </c>
       <c r="U15">
         <v>0</v>
@@ -1889,7 +1905,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1927,7 +1943,7 @@
         <v>565.04</v>
       </c>
       <c r="M16">
-        <v>295.29</v>
+        <v>295.29000000000002</v>
       </c>
       <c r="N16" t="s">
         <v>30</v>
@@ -1972,7 +1988,7 @@
         <v>565.04</v>
       </c>
       <c r="AB16">
-        <v>295.29</v>
+        <v>295.29000000000002</v>
       </c>
       <c r="AC16" t="s">
         <v>30</v>
@@ -1984,7 +2000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:31">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1995,7 +2011,7 @@
         <v>1.77</v>
       </c>
       <c r="D17">
-        <v>37.84</v>
+        <v>37.840000000000003</v>
       </c>
       <c r="E17">
         <v>74.36</v>
@@ -2040,7 +2056,7 @@
         <v>1.77</v>
       </c>
       <c r="S17">
-        <v>37.84</v>
+        <v>37.840000000000003</v>
       </c>
       <c r="T17">
         <v>74.36</v>
@@ -2079,7 +2095,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:31">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2117,7 +2133,7 @@
         <v>1016.96</v>
       </c>
       <c r="M18">
-        <v>574.58</v>
+        <v>574.58000000000004</v>
       </c>
       <c r="N18" t="s">
         <v>30</v>
@@ -2162,7 +2178,7 @@
         <v>1016.96</v>
       </c>
       <c r="AB18">
-        <v>574.58</v>
+        <v>574.58000000000004</v>
       </c>
       <c r="AC18" t="s">
         <v>30</v>
@@ -2174,7 +2190,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:31">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2185,7 +2201,7 @@
         <v>5.38</v>
       </c>
       <c r="D19">
-        <v>69.65000000000001</v>
+        <v>69.650000000000006</v>
       </c>
       <c r="E19">
         <v>86.7</v>
@@ -2230,7 +2246,7 @@
         <v>5.38</v>
       </c>
       <c r="S19">
-        <v>69.65000000000001</v>
+        <v>69.650000000000006</v>
       </c>
       <c r="T19">
         <v>86.7</v>
@@ -2269,7 +2285,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:31">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2364,7 +2380,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:31">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2459,7 +2475,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:31">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -2554,7 +2570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:31">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -2568,7 +2584,7 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>38.27</v>
+        <v>38.270000000000003</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2592,7 +2608,7 @@
         <v>864.53</v>
       </c>
       <c r="M23">
-        <v>987.9400000000001</v>
+        <v>987.94</v>
       </c>
       <c r="N23" t="s">
         <v>30</v>
@@ -2613,7 +2629,7 @@
         <v>29</v>
       </c>
       <c r="T23">
-        <v>38.27</v>
+        <v>38.270000000000003</v>
       </c>
       <c r="U23">
         <v>0</v>
@@ -2637,7 +2653,7 @@
         <v>864.53</v>
       </c>
       <c r="AB23">
-        <v>987.9400000000001</v>
+        <v>987.94</v>
       </c>
       <c r="AC23" t="s">
         <v>30</v>
@@ -2649,7 +2665,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:31">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -2684,7 +2700,7 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>1037.36</v>
+        <v>1037.3599999999999</v>
       </c>
       <c r="M24">
         <v>895.64</v>
@@ -2729,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>1037.36</v>
+        <v>1037.3599999999999</v>
       </c>
       <c r="AB24">
         <v>895.64</v>
@@ -2744,7 +2760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:31">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -2839,7 +2855,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:31">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -2874,7 +2890,7 @@
         <v>0.06</v>
       </c>
       <c r="L26">
-        <v>1207.12</v>
+        <v>1207.1199999999999</v>
       </c>
       <c r="M26">
         <v>130.87</v>
@@ -2919,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>1207.12</v>
+        <v>1207.1199999999999</v>
       </c>
       <c r="AB26">
         <v>130.87</v>
@@ -2934,7 +2950,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:31">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -2948,7 +2964,7 @@
         <v>44.45</v>
       </c>
       <c r="E27">
-        <v>32.7</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -2969,7 +2985,7 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>987.1900000000001</v>
+        <v>987.19</v>
       </c>
       <c r="M27">
         <v>774.74</v>
@@ -2993,7 +3009,7 @@
         <v>44.45</v>
       </c>
       <c r="T27">
-        <v>32.7</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="U27">
         <v>0</v>
@@ -3014,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>987.1900000000001</v>
+        <v>987.19</v>
       </c>
       <c r="AB27">
         <v>774.74</v>
@@ -3029,7 +3045,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:31">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -3049,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H28">
         <v>0.06</v>
@@ -3058,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K28">
         <v>0.23</v>
@@ -3067,7 +3083,7 @@
         <v>1205.49</v>
       </c>
       <c r="M28">
-        <v>306.53</v>
+        <v>306.52999999999997</v>
       </c>
       <c r="N28" t="s">
         <v>30</v>
@@ -3094,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="V28">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W28">
         <v>0.06</v>
@@ -3103,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="Y28">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Z28">
         <v>0.2</v>
@@ -3112,7 +3128,7 @@
         <v>1205.49</v>
       </c>
       <c r="AB28">
-        <v>306.53</v>
+        <v>306.52999999999997</v>
       </c>
       <c r="AC28" t="s">
         <v>30</v>
@@ -3124,7 +3140,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:31">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3219,7 +3235,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:31">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3314,7 +3330,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:31">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3325,7 +3341,7 @@
         <v>1.25</v>
       </c>
       <c r="D31">
-        <v>36.55</v>
+        <v>36.549999999999997</v>
       </c>
       <c r="E31">
         <v>58.38</v>
@@ -3352,7 +3368,7 @@
         <v>1328.92</v>
       </c>
       <c r="M31">
-        <v>748.9299999999999</v>
+        <v>748.93</v>
       </c>
       <c r="N31" t="s">
         <v>30</v>
@@ -3370,7 +3386,7 @@
         <v>1.25</v>
       </c>
       <c r="S31">
-        <v>36.55</v>
+        <v>36.549999999999997</v>
       </c>
       <c r="T31">
         <v>58.38</v>
@@ -3397,7 +3413,7 @@
         <v>1328.92</v>
       </c>
       <c r="AB31">
-        <v>748.9299999999999</v>
+        <v>748.93</v>
       </c>
       <c r="AC31" t="s">
         <v>30</v>
@@ -3409,7 +3425,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:31">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3420,7 +3436,7 @@
         <v>3.31</v>
       </c>
       <c r="D32">
-        <v>38.8</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="E32">
         <v>27.37</v>
@@ -3465,7 +3481,7 @@
         <v>3.31</v>
       </c>
       <c r="S32">
-        <v>38.8</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="T32">
         <v>27.37</v>
@@ -3504,7 +3520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:31">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3599,7 +3615,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:31">
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3607,7 +3623,7 @@
         <v>12578</v>
       </c>
       <c r="C34">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="D34">
         <v>23.23</v>
@@ -3652,7 +3668,7 @@
         <v>12578</v>
       </c>
       <c r="R34">
-        <v>2.07</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="S34">
         <v>23.23</v>
@@ -3694,7 +3710,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:31">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3714,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H35">
         <v>0.06</v>
@@ -3729,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>161.55</v>
+        <v>161.55000000000001</v>
       </c>
       <c r="M35">
         <v>144.4</v>
@@ -3759,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="V35">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W35">
         <v>0.06</v>
@@ -3774,7 +3790,7 @@
         <v>0.37</v>
       </c>
       <c r="AA35">
-        <v>161.55</v>
+        <v>161.55000000000001</v>
       </c>
       <c r="AB35">
         <v>144.4</v>
@@ -3789,7 +3805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:31">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -3800,10 +3816,10 @@
         <v>3.42</v>
       </c>
       <c r="D36">
-        <v>36.48</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="E36">
-        <v>80.40000000000001</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -3845,10 +3861,10 @@
         <v>3.42</v>
       </c>
       <c r="S36">
-        <v>36.48</v>
+        <v>36.479999999999997</v>
       </c>
       <c r="T36">
-        <v>80.40000000000001</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="U36">
         <v>0</v>
@@ -3884,7 +3900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:31">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -3898,7 +3914,7 @@
         <v>74.25</v>
       </c>
       <c r="E37">
-        <v>73.90000000000001</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -3943,7 +3959,7 @@
         <v>74.25</v>
       </c>
       <c r="T37">
-        <v>73.90000000000001</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="U37">
         <v>0</v>
@@ -3979,7 +3995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:31">
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3990,7 +4006,7 @@
         <v>3.83</v>
       </c>
       <c r="D38">
-        <v>37.66</v>
+        <v>37.659999999999997</v>
       </c>
       <c r="E38">
         <v>88.62</v>
@@ -4014,10 +4030,10 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>260.22</v>
+        <v>260.22000000000003</v>
       </c>
       <c r="M38">
-        <v>647.6799999999999</v>
+        <v>647.67999999999995</v>
       </c>
       <c r="N38" t="s">
         <v>30</v>
@@ -4035,7 +4051,7 @@
         <v>3.83</v>
       </c>
       <c r="S38">
-        <v>37.66</v>
+        <v>37.659999999999997</v>
       </c>
       <c r="T38">
         <v>88.62</v>
@@ -4059,10 +4075,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>260.22</v>
+        <v>260.22000000000003</v>
       </c>
       <c r="AB38">
-        <v>647.6799999999999</v>
+        <v>647.67999999999995</v>
       </c>
       <c r="AC38" t="s">
         <v>30</v>
@@ -4074,7 +4090,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:31">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -4169,7 +4185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:31">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -4180,7 +4196,7 @@
         <v>3.48</v>
       </c>
       <c r="D40">
-        <v>33.62</v>
+        <v>33.619999999999997</v>
       </c>
       <c r="E40">
         <v>21.19</v>
@@ -4225,7 +4241,7 @@
         <v>3.48</v>
       </c>
       <c r="S40">
-        <v>33.62</v>
+        <v>33.619999999999997</v>
       </c>
       <c r="T40">
         <v>21.19</v>
@@ -4264,7 +4280,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:31">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -4278,7 +4294,7 @@
         <v>40.32</v>
       </c>
       <c r="E41">
-        <v>64.59999999999999</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -4323,7 +4339,7 @@
         <v>40.32</v>
       </c>
       <c r="T41">
-        <v>64.59999999999999</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -4359,7 +4375,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:31">
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -4367,7 +4383,7 @@
         <v>43203</v>
       </c>
       <c r="C42">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="D42">
         <v>17.84</v>
@@ -4412,7 +4428,7 @@
         <v>43203</v>
       </c>
       <c r="R42">
-        <v>9.779999999999999</v>
+        <v>9.7799999999999994</v>
       </c>
       <c r="S42">
         <v>17.84</v>
@@ -4433,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="Y42">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4454,7 +4470,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:31">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -4468,13 +4484,13 @@
         <v>53.85</v>
       </c>
       <c r="E43">
-        <v>76.59999999999999</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="F43">
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H43">
         <v>0.06</v>
@@ -4513,13 +4529,13 @@
         <v>53.85</v>
       </c>
       <c r="T43">
-        <v>76.59999999999999</v>
+        <v>76.599999999999994</v>
       </c>
       <c r="U43">
         <v>0</v>
       </c>
       <c r="V43">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W43">
         <v>0.06</v>
@@ -4549,7 +4565,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:31">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -4644,7 +4660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:31">
+    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -4652,7 +4668,7 @@
         <v>42820</v>
       </c>
       <c r="C45">
-        <v>8.029999999999999</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="D45">
         <v>71.92</v>
@@ -4682,7 +4698,7 @@
         <v>747.8</v>
       </c>
       <c r="M45">
-        <v>603.95</v>
+        <v>603.95000000000005</v>
       </c>
       <c r="N45" t="s">
         <v>30</v>
@@ -4697,7 +4713,7 @@
         <v>42820</v>
       </c>
       <c r="R45">
-        <v>8.029999999999999</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="S45">
         <v>71.92</v>
@@ -4727,7 +4743,7 @@
         <v>747.8</v>
       </c>
       <c r="AB45">
-        <v>603.95</v>
+        <v>603.95000000000005</v>
       </c>
       <c r="AC45" t="s">
         <v>30</v>
@@ -4739,7 +4755,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:31">
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -4774,10 +4790,10 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>616.58</v>
+        <v>616.58000000000004</v>
       </c>
       <c r="M46">
-        <v>79.48999999999999</v>
+        <v>79.489999999999995</v>
       </c>
       <c r="N46" t="s">
         <v>30</v>
@@ -4819,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>616.58</v>
+        <v>616.58000000000004</v>
       </c>
       <c r="AB46">
-        <v>79.48999999999999</v>
+        <v>79.489999999999995</v>
       </c>
       <c r="AC46" t="s">
         <v>30</v>
@@ -4834,7 +4850,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:31">
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -4863,13 +4879,13 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>899.0700000000001</v>
+        <v>899.07</v>
       </c>
       <c r="M47">
         <v>852.77</v>
@@ -4914,7 +4930,7 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>899.0700000000001</v>
+        <v>899.07</v>
       </c>
       <c r="AB47">
         <v>852.77</v>
@@ -4929,7 +4945,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="48" spans="1:31">
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -4967,7 +4983,7 @@
         <v>607.09</v>
       </c>
       <c r="M48">
-        <v>299.29</v>
+        <v>299.29000000000002</v>
       </c>
       <c r="N48" t="s">
         <v>30</v>
@@ -5012,7 +5028,7 @@
         <v>607.09</v>
       </c>
       <c r="AB48">
-        <v>299.29</v>
+        <v>299.29000000000002</v>
       </c>
       <c r="AC48" t="s">
         <v>30</v>
@@ -5024,7 +5040,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:31">
+    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -5119,7 +5135,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:31">
+    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -5148,13 +5164,13 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K50">
         <v>0.02</v>
       </c>
       <c r="L50">
-        <v>882.0599999999999</v>
+        <v>882.06</v>
       </c>
       <c r="M50">
         <v>60.16</v>
@@ -5196,10 +5212,10 @@
         <v>0.22</v>
       </c>
       <c r="Z50">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA50">
-        <v>882.0599999999999</v>
+        <v>882.06</v>
       </c>
       <c r="AB50">
         <v>60.16</v>
@@ -5214,7 +5230,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="51" spans="1:31">
+    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -5309,7 +5325,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:31">
+    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -5317,7 +5333,7 @@
         <v>53101</v>
       </c>
       <c r="C52">
-        <v>4.39</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="D52">
         <v>50.25</v>
@@ -5362,7 +5378,7 @@
         <v>53101</v>
       </c>
       <c r="R52">
-        <v>4.39</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="S52">
         <v>50.25</v>
@@ -5404,7 +5420,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:31">
+    <row r="53" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -5442,7 +5458,7 @@
         <v>1224.44</v>
       </c>
       <c r="M53">
-        <v>650.0599999999999</v>
+        <v>650.05999999999995</v>
       </c>
       <c r="N53" t="s">
         <v>30</v>
@@ -5487,7 +5503,7 @@
         <v>1224.44</v>
       </c>
       <c r="AB53">
-        <v>650.0599999999999</v>
+        <v>650.05999999999995</v>
       </c>
       <c r="AC53" t="s">
         <v>30</v>
@@ -5499,7 +5515,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="54" spans="1:31">
+    <row r="54" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -5573,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="Y54">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5594,7 +5610,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:31">
+    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -5605,7 +5621,7 @@
         <v>3.63</v>
       </c>
       <c r="D55">
-        <v>39.62</v>
+        <v>39.619999999999997</v>
       </c>
       <c r="E55">
         <v>50.57</v>
@@ -5623,13 +5639,13 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K55">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L55">
-        <v>1255.14</v>
+        <v>1255.1400000000001</v>
       </c>
       <c r="M55">
         <v>878.85</v>
@@ -5650,7 +5666,7 @@
         <v>3.63</v>
       </c>
       <c r="S55">
-        <v>39.62</v>
+        <v>39.619999999999997</v>
       </c>
       <c r="T55">
         <v>50.57</v>
@@ -5671,10 +5687,10 @@
         <v>0.06</v>
       </c>
       <c r="Z55">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AA55">
-        <v>1255.14</v>
+        <v>1255.1400000000001</v>
       </c>
       <c r="AB55">
         <v>878.85</v>
@@ -5689,7 +5705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:31">
+    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -5709,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="H56">
         <v>0.31</v>
@@ -5754,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="V56">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="W56">
         <v>0.31</v>
@@ -5784,7 +5800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:31">
+    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>55</v>
       </c>
@@ -5879,7 +5895,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="58" spans="1:31">
+    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -5974,7 +5990,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:31">
+    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -6069,7 +6085,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="60" spans="1:31">
+    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>58</v>
       </c>
@@ -6164,7 +6180,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:31">
+    <row r="61" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>59</v>
       </c>
@@ -6172,7 +6188,7 @@
         <v>43433</v>
       </c>
       <c r="C61">
-        <v>4.52</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="D61">
         <v>28.63</v>
@@ -6199,7 +6215,7 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>257.22</v>
+        <v>257.22000000000003</v>
       </c>
       <c r="M61">
         <v>336.06</v>
@@ -6217,7 +6233,7 @@
         <v>43433</v>
       </c>
       <c r="R61">
-        <v>4.52</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="S61">
         <v>28.63</v>
@@ -6244,7 +6260,7 @@
         <v>0</v>
       </c>
       <c r="AA61">
-        <v>257.22</v>
+        <v>257.22000000000003</v>
       </c>
       <c r="AB61">
         <v>336.06</v>
@@ -6259,7 +6275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:31">
+    <row r="62" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -6354,7 +6370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:31">
+    <row r="63" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -6392,7 +6408,7 @@
         <v>88.13</v>
       </c>
       <c r="M63">
-        <v>587.55</v>
+        <v>587.54999999999995</v>
       </c>
       <c r="N63" t="s">
         <v>30</v>
@@ -6437,7 +6453,7 @@
         <v>88.13</v>
       </c>
       <c r="AB63">
-        <v>587.55</v>
+        <v>587.54999999999995</v>
       </c>
       <c r="AC63" t="s">
         <v>30</v>
@@ -6449,7 +6465,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:31">
+    <row r="64" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -6469,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H64">
         <v>0.06</v>
@@ -6514,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="V64">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W64">
         <v>0.06</v>
@@ -6544,7 +6560,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:31">
+    <row r="65" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -6552,10 +6568,10 @@
         <v>6338</v>
       </c>
       <c r="C65">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="D65">
-        <v>8.789999999999999</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="E65">
         <v>7.34</v>
@@ -6567,7 +6583,7 @@
         <v>0.71</v>
       </c>
       <c r="H65">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -6597,10 +6613,10 @@
         <v>6338</v>
       </c>
       <c r="R65">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="S65">
-        <v>8.789999999999999</v>
+        <v>8.7899999999999991</v>
       </c>
       <c r="T65">
         <v>7.34</v>
@@ -6612,7 +6628,7 @@
         <v>0.71</v>
       </c>
       <c r="W65">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="X65">
         <v>0</v>
@@ -6639,7 +6655,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:31">
+    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -6734,7 +6750,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:31">
+    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -6745,7 +6761,7 @@
         <v>6.38</v>
       </c>
       <c r="D67">
-        <v>40.12</v>
+        <v>40.119999999999997</v>
       </c>
       <c r="E67">
         <v>44.22</v>
@@ -6790,7 +6806,7 @@
         <v>6.38</v>
       </c>
       <c r="S67">
-        <v>40.12</v>
+        <v>40.119999999999997</v>
       </c>
       <c r="T67">
         <v>44.22</v>
@@ -6808,7 +6824,7 @@
         <v>0</v>
       </c>
       <c r="Y67">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6829,7 +6845,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:31">
+    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -6840,7 +6856,7 @@
         <v>5.63</v>
       </c>
       <c r="D68">
-        <v>37.34</v>
+        <v>37.340000000000003</v>
       </c>
       <c r="E68">
         <v>42.83</v>
@@ -6849,7 +6865,7 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="H68">
         <v>0.19</v>
@@ -6885,7 +6901,7 @@
         <v>5.63</v>
       </c>
       <c r="S68">
-        <v>37.34</v>
+        <v>37.340000000000003</v>
       </c>
       <c r="T68">
         <v>42.83</v>
@@ -6894,7 +6910,7 @@
         <v>0</v>
       </c>
       <c r="V68">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="W68">
         <v>0.19</v>
@@ -6924,7 +6940,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:31">
+    <row r="69" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -6932,7 +6948,7 @@
         <v>64346</v>
       </c>
       <c r="C69">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="D69">
         <v>27.35</v>
@@ -6977,7 +6993,7 @@
         <v>64346</v>
       </c>
       <c r="R69">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="S69">
         <v>27.35</v>
@@ -7019,7 +7035,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:31">
+    <row r="70" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -7054,10 +7070,10 @@
         <v>0.04</v>
       </c>
       <c r="L70">
-        <v>303.53</v>
+        <v>303.52999999999997</v>
       </c>
       <c r="M70">
-        <v>82.40000000000001</v>
+        <v>82.4</v>
       </c>
       <c r="N70" t="s">
         <v>30</v>
@@ -7099,10 +7115,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>303.53</v>
+        <v>303.52999999999997</v>
       </c>
       <c r="AB70">
-        <v>82.40000000000001</v>
+        <v>82.4</v>
       </c>
       <c r="AC70" t="s">
         <v>30</v>
@@ -7114,7 +7130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:31">
+    <row r="71" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>69</v>
       </c>
@@ -7209,7 +7225,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:31">
+    <row r="72" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -7223,7 +7239,7 @@
         <v>52.36</v>
       </c>
       <c r="E72">
-        <v>76.73999999999999</v>
+        <v>76.739999999999995</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -7268,7 +7284,7 @@
         <v>52.36</v>
       </c>
       <c r="T72">
-        <v>76.73999999999999</v>
+        <v>76.739999999999995</v>
       </c>
       <c r="U72">
         <v>0</v>
@@ -7304,7 +7320,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:31">
+    <row r="73" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -7399,7 +7415,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:31">
+    <row r="74" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -7413,7 +7429,7 @@
         <v>53.11</v>
       </c>
       <c r="E74">
-        <v>71.20999999999999</v>
+        <v>71.209999999999994</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -7437,7 +7453,7 @@
         <v>812.72</v>
       </c>
       <c r="M74">
-        <v>636.4299999999999</v>
+        <v>636.42999999999995</v>
       </c>
       <c r="N74" t="s">
         <v>30</v>
@@ -7458,7 +7474,7 @@
         <v>53.11</v>
       </c>
       <c r="T74">
-        <v>71.20999999999999</v>
+        <v>71.209999999999994</v>
       </c>
       <c r="U74">
         <v>0</v>
@@ -7482,7 +7498,7 @@
         <v>812.72</v>
       </c>
       <c r="AB74">
-        <v>636.4299999999999</v>
+        <v>636.42999999999995</v>
       </c>
       <c r="AC74" t="s">
         <v>30</v>
@@ -7494,7 +7510,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:31">
+    <row r="75" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -7529,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="L75">
-        <v>554.42</v>
+        <v>554.41999999999996</v>
       </c>
       <c r="M75">
-        <v>548.42</v>
+        <v>548.41999999999996</v>
       </c>
       <c r="N75" t="s">
         <v>30</v>
@@ -7574,10 +7590,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>554.42</v>
+        <v>554.41999999999996</v>
       </c>
       <c r="AB75">
-        <v>548.42</v>
+        <v>548.41999999999996</v>
       </c>
       <c r="AC75" t="s">
         <v>30</v>
@@ -7589,7 +7605,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="76" spans="1:31">
+    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -7600,16 +7616,16 @@
         <v>5.95</v>
       </c>
       <c r="D76">
-        <v>67.34999999999999</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="E76">
-        <v>77.34999999999999</v>
+        <v>77.349999999999994</v>
       </c>
       <c r="F76">
         <v>0</v>
       </c>
       <c r="G76">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H76">
         <v>0.06</v>
@@ -7645,16 +7661,16 @@
         <v>5.95</v>
       </c>
       <c r="S76">
-        <v>67.34999999999999</v>
+        <v>67.349999999999994</v>
       </c>
       <c r="T76">
-        <v>77.34999999999999</v>
+        <v>77.349999999999994</v>
       </c>
       <c r="U76">
         <v>0</v>
       </c>
       <c r="V76">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W76">
         <v>0.06</v>
@@ -7684,7 +7700,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="77" spans="1:31">
+    <row r="77" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -7758,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="Y77">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7779,7 +7795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:31">
+    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -7790,10 +7806,10 @@
         <v>4.22</v>
       </c>
       <c r="D78">
-        <v>67.45999999999999</v>
+        <v>67.459999999999994</v>
       </c>
       <c r="E78">
-        <v>68.59999999999999</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -7835,10 +7851,10 @@
         <v>4.22</v>
       </c>
       <c r="S78">
-        <v>67.45999999999999</v>
+        <v>67.459999999999994</v>
       </c>
       <c r="T78">
-        <v>68.59999999999999</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="U78">
         <v>0</v>
@@ -7874,7 +7890,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:31">
+    <row r="79" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>77</v>
       </c>
@@ -7969,7 +7985,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="80" spans="1:31">
+    <row r="80" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -8064,7 +8080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:31">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -8159,7 +8175,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:31">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -8194,7 +8210,7 @@
         <v>0</v>
       </c>
       <c r="L82">
-        <v>1217.84</v>
+        <v>1217.8399999999999</v>
       </c>
       <c r="M82">
         <v>274.81</v>
@@ -8239,7 +8255,7 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>1217.84</v>
+        <v>1217.8399999999999</v>
       </c>
       <c r="AB82">
         <v>274.81</v>
@@ -8254,7 +8270,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:31">
+    <row r="83" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -8268,7 +8284,7 @@
         <v>22.65</v>
       </c>
       <c r="E83">
-        <v>35.62</v>
+        <v>35.619999999999997</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -8313,7 +8329,7 @@
         <v>22.65</v>
       </c>
       <c r="T83">
-        <v>35.62</v>
+        <v>35.619999999999997</v>
       </c>
       <c r="U83">
         <v>0</v>
@@ -8349,7 +8365,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:31">
+    <row r="84" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>82</v>
       </c>
@@ -8357,10 +8373,10 @@
         <v>15485</v>
       </c>
       <c r="C84">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="D84">
-        <v>16.76</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="E84">
         <v>22.21</v>
@@ -8402,10 +8418,10 @@
         <v>15485</v>
       </c>
       <c r="R84">
-        <v>2.3</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="S84">
-        <v>16.76</v>
+        <v>16.760000000000002</v>
       </c>
       <c r="T84">
         <v>22.21</v>
@@ -8444,7 +8460,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="85" spans="1:31">
+    <row r="85" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -8482,7 +8498,7 @@
         <v>1361.61</v>
       </c>
       <c r="M85">
-        <v>558.3200000000001</v>
+        <v>558.32000000000005</v>
       </c>
       <c r="N85" t="s">
         <v>30</v>
@@ -8527,7 +8543,7 @@
         <v>1361.61</v>
       </c>
       <c r="AB85">
-        <v>558.3200000000001</v>
+        <v>558.32000000000005</v>
       </c>
       <c r="AC85" t="s">
         <v>30</v>
@@ -8539,7 +8555,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="86" spans="1:31">
+    <row r="86" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -8553,7 +8569,7 @@
         <v>49.67</v>
       </c>
       <c r="E86">
-        <v>78.26000000000001</v>
+        <v>78.260000000000005</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -8598,7 +8614,7 @@
         <v>49.67</v>
       </c>
       <c r="T86">
-        <v>78.26000000000001</v>
+        <v>78.260000000000005</v>
       </c>
       <c r="U86">
         <v>0</v>
@@ -8634,7 +8650,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="87" spans="1:31">
+    <row r="87" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -8648,7 +8664,7 @@
         <v>37.15</v>
       </c>
       <c r="E87">
-        <v>39.09</v>
+        <v>39.090000000000003</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -8693,7 +8709,7 @@
         <v>37.15</v>
       </c>
       <c r="T87">
-        <v>39.09</v>
+        <v>39.090000000000003</v>
       </c>
       <c r="U87">
         <v>0</v>
@@ -8729,7 +8745,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" spans="1:31">
+    <row r="88" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -8737,7 +8753,7 @@
         <v>33863</v>
       </c>
       <c r="C88">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="D88">
         <v>31.02</v>
@@ -8782,7 +8798,7 @@
         <v>33863</v>
       </c>
       <c r="R88">
-        <v>2.28</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="S88">
         <v>31.02</v>
@@ -8824,7 +8840,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:31">
+    <row r="89" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -8919,7 +8935,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="90" spans="1:31">
+    <row r="90" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -9014,7 +9030,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:31">
+    <row r="91" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -9109,7 +9125,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:31">
+    <row r="92" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -9204,7 +9220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:31">
+    <row r="93" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>91</v>
       </c>
@@ -9299,7 +9315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:31">
+    <row r="94" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -9313,7 +9329,7 @@
         <v>67.14</v>
       </c>
       <c r="E94">
-        <v>86.98999999999999</v>
+        <v>86.99</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -9358,7 +9374,7 @@
         <v>67.14</v>
       </c>
       <c r="T94">
-        <v>86.98999999999999</v>
+        <v>86.99</v>
       </c>
       <c r="U94">
         <v>0</v>
@@ -9373,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Z94">
         <v>0.24</v>
@@ -9394,7 +9410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:31">
+    <row r="95" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -9489,7 +9505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:31">
+    <row r="96" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -9566,7 +9582,7 @@
         <v>0.2</v>
       </c>
       <c r="Z96">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA96">
         <v>248.98</v>
@@ -9584,7 +9600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:31">
+    <row r="97" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -9595,7 +9611,7 @@
         <v>2.68</v>
       </c>
       <c r="D97">
-        <v>39.87</v>
+        <v>39.869999999999997</v>
       </c>
       <c r="E97">
         <v>25.73</v>
@@ -9622,7 +9638,7 @@
         <v>213.87</v>
       </c>
       <c r="M97">
-        <v>823.6900000000001</v>
+        <v>823.69</v>
       </c>
       <c r="N97" t="s">
         <v>30</v>
@@ -9640,7 +9656,7 @@
         <v>2.68</v>
       </c>
       <c r="S97">
-        <v>39.87</v>
+        <v>39.869999999999997</v>
       </c>
       <c r="T97">
         <v>25.73</v>
@@ -9667,7 +9683,7 @@
         <v>213.87</v>
       </c>
       <c r="AB97">
-        <v>823.6900000000001</v>
+        <v>823.69</v>
       </c>
       <c r="AC97" t="s">
         <v>30</v>
@@ -9679,7 +9695,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:31">
+    <row r="98" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -9774,7 +9790,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:31">
+    <row r="99" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -9869,7 +9885,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:31">
+    <row r="100" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -9964,7 +9980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:31">
+    <row r="101" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -9972,13 +9988,13 @@
         <v>8786</v>
       </c>
       <c r="C101">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="D101">
         <v>123.74</v>
       </c>
       <c r="E101">
-        <v>131.67</v>
+        <v>131.66999999999999</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -10002,7 +10018,7 @@
         <v>459.54</v>
       </c>
       <c r="M101">
-        <v>514.4299999999999</v>
+        <v>514.42999999999995</v>
       </c>
       <c r="N101" t="s">
         <v>30</v>
@@ -10017,13 +10033,13 @@
         <v>8786</v>
       </c>
       <c r="R101">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="S101">
         <v>123.74</v>
       </c>
       <c r="T101">
-        <v>131.67</v>
+        <v>131.66999999999999</v>
       </c>
       <c r="U101">
         <v>0</v>
@@ -10047,7 +10063,7 @@
         <v>459.54</v>
       </c>
       <c r="AB101">
-        <v>514.4299999999999</v>
+        <v>514.42999999999995</v>
       </c>
       <c r="AC101" t="s">
         <v>30</v>
@@ -10059,7 +10075,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:31">
+    <row r="102" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -10073,13 +10089,13 @@
         <v>50.07</v>
       </c>
       <c r="E102">
-        <v>72.68000000000001</v>
+        <v>72.680000000000007</v>
       </c>
       <c r="F102">
         <v>0</v>
       </c>
       <c r="G102">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H102">
         <v>0.06</v>
@@ -10118,13 +10134,13 @@
         <v>50.07</v>
       </c>
       <c r="T102">
-        <v>72.68000000000001</v>
+        <v>72.680000000000007</v>
       </c>
       <c r="U102">
         <v>0</v>
       </c>
       <c r="V102">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W102">
         <v>0.06</v>
@@ -10154,7 +10170,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:31">
+    <row r="103" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>101</v>
       </c>
@@ -10174,7 +10190,7 @@
         <v>0</v>
       </c>
       <c r="G103">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="H103">
         <v>0.43</v>
@@ -10219,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="V103">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="W103">
         <v>0.43</v>
@@ -10231,7 +10247,7 @@
         <v>0.52</v>
       </c>
       <c r="Z103">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA103">
         <v>785.2</v>
@@ -10249,7 +10265,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:31">
+    <row r="104" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -10263,7 +10279,7 @@
         <v>79.48</v>
       </c>
       <c r="E104">
-        <v>97.26000000000001</v>
+        <v>97.26</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -10308,7 +10324,7 @@
         <v>79.48</v>
       </c>
       <c r="T104">
-        <v>97.26000000000001</v>
+        <v>97.26</v>
       </c>
       <c r="U104">
         <v>0</v>
@@ -10344,7 +10360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:31">
+    <row r="105" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -10379,7 +10395,7 @@
         <v>0.35</v>
       </c>
       <c r="L105">
-        <v>816.8099999999999</v>
+        <v>816.81</v>
       </c>
       <c r="M105">
         <v>654.37</v>
@@ -10424,7 +10440,7 @@
         <v>0.27</v>
       </c>
       <c r="AA105">
-        <v>816.8099999999999</v>
+        <v>816.81</v>
       </c>
       <c r="AB105">
         <v>654.37</v>
@@ -10439,7 +10455,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:31">
+    <row r="106" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -10453,7 +10469,7 @@
         <v>56.57</v>
       </c>
       <c r="E106">
-        <v>86.48999999999999</v>
+        <v>86.49</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -10462,7 +10478,7 @@
         <v>0.93</v>
       </c>
       <c r="H106">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I106">
         <v>0</v>
@@ -10498,7 +10514,7 @@
         <v>56.57</v>
       </c>
       <c r="T106">
-        <v>86.48999999999999</v>
+        <v>86.49</v>
       </c>
       <c r="U106">
         <v>0</v>
@@ -10507,7 +10523,7 @@
         <v>0.93</v>
       </c>
       <c r="W106">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X106">
         <v>0</v>
@@ -10534,7 +10550,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="107" spans="1:31">
+    <row r="107" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -10548,7 +10564,7 @@
         <v>48.83</v>
       </c>
       <c r="E107">
-        <v>70.68000000000001</v>
+        <v>70.680000000000007</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -10593,7 +10609,7 @@
         <v>48.83</v>
       </c>
       <c r="T107">
-        <v>70.68000000000001</v>
+        <v>70.680000000000007</v>
       </c>
       <c r="U107">
         <v>0</v>
@@ -10629,7 +10645,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:31">
+    <row r="108" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -10643,7 +10659,7 @@
         <v>58.73</v>
       </c>
       <c r="E108">
-        <v>94.01000000000001</v>
+        <v>94.01</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -10688,7 +10704,7 @@
         <v>58.73</v>
       </c>
       <c r="T108">
-        <v>94.01000000000001</v>
+        <v>94.01</v>
       </c>
       <c r="U108">
         <v>0</v>
@@ -10724,7 +10740,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:31">
+    <row r="109" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>107</v>
       </c>
@@ -10819,7 +10835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:31">
+    <row r="110" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -10827,7 +10843,7 @@
         <v>49877</v>
       </c>
       <c r="C110">
-        <v>5.06</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="D110">
         <v>51.29</v>
@@ -10872,7 +10888,7 @@
         <v>49877</v>
       </c>
       <c r="R110">
-        <v>5.06</v>
+        <v>5.0599999999999996</v>
       </c>
       <c r="S110">
         <v>51.29</v>
@@ -10914,7 +10930,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="111" spans="1:31">
+    <row r="111" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -10937,7 +10953,7 @@
         <v>0.72</v>
       </c>
       <c r="H111">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -10949,7 +10965,7 @@
         <v>0.03</v>
       </c>
       <c r="L111">
-        <v>1105.39</v>
+        <v>1105.3900000000001</v>
       </c>
       <c r="M111">
         <v>970.24</v>
@@ -10982,7 +10998,7 @@
         <v>0.72</v>
       </c>
       <c r="W111">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="X111">
         <v>0</v>
@@ -10994,7 +11010,7 @@
         <v>0.46</v>
       </c>
       <c r="AA111">
-        <v>1105.39</v>
+        <v>1105.3900000000001</v>
       </c>
       <c r="AB111">
         <v>970.24</v>
@@ -11009,7 +11025,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="1:31">
+    <row r="112" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -11083,7 +11099,7 @@
         <v>0</v>
       </c>
       <c r="Y112">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Z112">
         <v>0.61</v>
@@ -11104,7 +11120,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:31">
+    <row r="113" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -11199,7 +11215,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:31">
+    <row r="114" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -11294,7 +11310,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="115" spans="1:31">
+    <row r="115" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -11302,7 +11318,7 @@
         <v>15898</v>
       </c>
       <c r="C115">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="D115">
         <v>46.64</v>
@@ -11317,7 +11333,7 @@
         <v>0.86</v>
       </c>
       <c r="H115">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I115">
         <v>0</v>
@@ -11347,7 +11363,7 @@
         <v>15898</v>
       </c>
       <c r="R115">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="S115">
         <v>46.64</v>
@@ -11362,7 +11378,7 @@
         <v>0.86</v>
       </c>
       <c r="W115">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="X115">
         <v>0</v>
@@ -11389,7 +11405,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="116" spans="1:31">
+    <row r="116" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>114</v>
       </c>
@@ -11463,7 +11479,7 @@
         <v>0</v>
       </c>
       <c r="Y116">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Z116">
         <v>0.15</v>
@@ -11484,7 +11500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:31">
+    <row r="117" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -11519,7 +11535,7 @@
         <v>1</v>
       </c>
       <c r="L117">
-        <v>89.29000000000001</v>
+        <v>89.29</v>
       </c>
       <c r="M117">
         <v>665.46</v>
@@ -11564,7 +11580,7 @@
         <v>1</v>
       </c>
       <c r="AA117">
-        <v>89.29000000000001</v>
+        <v>89.29</v>
       </c>
       <c r="AB117">
         <v>665.46</v>
@@ -11579,7 +11595,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:31">
+    <row r="118" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -11599,7 +11615,7 @@
         <v>0</v>
       </c>
       <c r="G118">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="H118">
         <v>0.19</v>
@@ -11644,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="V118">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="W118">
         <v>0.19</v>
@@ -11674,7 +11690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:31">
+    <row r="119" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -11682,7 +11698,7 @@
         <v>9373</v>
       </c>
       <c r="C119">
-        <v>2.53</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="D119">
         <v>25.16</v>
@@ -11697,7 +11713,7 @@
         <v>0.93</v>
       </c>
       <c r="H119">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -11709,10 +11725,10 @@
         <v>0</v>
       </c>
       <c r="L119">
-        <v>92.31999999999999</v>
+        <v>92.32</v>
       </c>
       <c r="M119">
-        <v>1053.09</v>
+        <v>1053.0899999999999</v>
       </c>
       <c r="N119" t="s">
         <v>30</v>
@@ -11727,7 +11743,7 @@
         <v>9373</v>
       </c>
       <c r="R119">
-        <v>2.53</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="S119">
         <v>25.16</v>
@@ -11742,7 +11758,7 @@
         <v>0.93</v>
       </c>
       <c r="W119">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="X119">
         <v>0</v>
@@ -11754,10 +11770,10 @@
         <v>0.77</v>
       </c>
       <c r="AA119">
-        <v>92.31999999999999</v>
+        <v>92.32</v>
       </c>
       <c r="AB119">
-        <v>1053.09</v>
+        <v>1053.0899999999999</v>
       </c>
       <c r="AC119" t="s">
         <v>30</v>
@@ -11769,7 +11785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:31">
+    <row r="120" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -11792,7 +11808,7 @@
         <v>0.86</v>
       </c>
       <c r="H120">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I120">
         <v>0</v>
@@ -11837,7 +11853,7 @@
         <v>0.86</v>
       </c>
       <c r="W120">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="X120">
         <v>0</v>
@@ -11864,7 +11880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="121" spans="1:31">
+    <row r="121" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -11893,7 +11909,7 @@
         <v>0</v>
       </c>
       <c r="J121">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K121">
         <v>0.04</v>
@@ -11959,7 +11975,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:31">
+    <row r="122" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -12054,7 +12070,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:31">
+    <row r="123" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>121</v>
       </c>
@@ -12068,13 +12084,13 @@
         <v>51.43</v>
       </c>
       <c r="E123">
-        <v>64.51000000000001</v>
+        <v>64.510000000000005</v>
       </c>
       <c r="F123">
         <v>0</v>
       </c>
       <c r="G123">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H123">
         <v>0.06</v>
@@ -12113,13 +12129,13 @@
         <v>51.43</v>
       </c>
       <c r="T123">
-        <v>64.51000000000001</v>
+        <v>64.510000000000005</v>
       </c>
       <c r="U123">
         <v>0</v>
       </c>
       <c r="V123">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W123">
         <v>0.06</v>
@@ -12149,7 +12165,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:31">
+    <row r="124" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -12187,7 +12203,7 @@
         <v>282.01</v>
       </c>
       <c r="M124">
-        <v>162.67</v>
+        <v>162.66999999999999</v>
       </c>
       <c r="N124" t="s">
         <v>30</v>
@@ -12232,7 +12248,7 @@
         <v>282.01</v>
       </c>
       <c r="AB124">
-        <v>162.67</v>
+        <v>162.66999999999999</v>
       </c>
       <c r="AC124" t="s">
         <v>30</v>
@@ -12244,7 +12260,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:31">
+    <row r="125" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -12339,7 +12355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:31">
+    <row r="126" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -12434,7 +12450,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:31">
+    <row r="127" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -12529,7 +12545,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="128" spans="1:31">
+    <row r="128" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -12567,7 +12583,7 @@
         <v>654.78</v>
       </c>
       <c r="M128">
-        <v>68.31999999999999</v>
+        <v>68.319999999999993</v>
       </c>
       <c r="N128" t="s">
         <v>30</v>
@@ -12612,7 +12628,7 @@
         <v>654.78</v>
       </c>
       <c r="AB128">
-        <v>68.31999999999999</v>
+        <v>68.319999999999993</v>
       </c>
       <c r="AC128" t="s">
         <v>30</v>
@@ -12624,7 +12640,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="129" spans="1:31">
+    <row r="129" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -12719,7 +12735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="1:31">
+    <row r="130" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -12739,7 +12755,7 @@
         <v>0</v>
       </c>
       <c r="G130">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="H130">
         <v>0.06</v>
@@ -12784,7 +12800,7 @@
         <v>0</v>
       </c>
       <c r="V130">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="W130">
         <v>0.06</v>
@@ -12814,7 +12830,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:31">
+    <row r="131" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -12909,7 +12925,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="132" spans="1:31">
+    <row r="132" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -12947,7 +12963,7 @@
         <v>906.42</v>
       </c>
       <c r="M132">
-        <v>546.42</v>
+        <v>546.41999999999996</v>
       </c>
       <c r="N132" t="s">
         <v>30</v>
@@ -12992,7 +13008,7 @@
         <v>906.42</v>
       </c>
       <c r="AB132">
-        <v>546.42</v>
+        <v>546.41999999999996</v>
       </c>
       <c r="AC132" t="s">
         <v>30</v>
@@ -13004,7 +13020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="133" spans="1:31">
+    <row r="133" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -13099,7 +13115,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:31">
+    <row r="134" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -13134,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="L134">
-        <v>1095.63</v>
+        <v>1095.6300000000001</v>
       </c>
       <c r="M134">
         <v>133.62</v>
@@ -13179,7 +13195,7 @@
         <v>0.52</v>
       </c>
       <c r="AA134">
-        <v>1095.63</v>
+        <v>1095.6300000000001</v>
       </c>
       <c r="AB134">
         <v>133.62</v>
@@ -13194,7 +13210,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="135" spans="1:31">
+    <row r="135" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -13289,7 +13305,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136" spans="1:31">
+    <row r="136" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -13303,7 +13319,7 @@
         <v>46.48</v>
       </c>
       <c r="E136">
-        <v>33.73</v>
+        <v>33.729999999999997</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -13348,7 +13364,7 @@
         <v>46.48</v>
       </c>
       <c r="T136">
-        <v>33.73</v>
+        <v>33.729999999999997</v>
       </c>
       <c r="U136">
         <v>0</v>
@@ -13384,7 +13400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:31">
+    <row r="137" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -13479,7 +13495,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="138" spans="1:31">
+    <row r="138" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -13574,7 +13590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="139" spans="1:31">
+    <row r="139" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -13651,7 +13667,7 @@
         <v>0.23</v>
       </c>
       <c r="Z139">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA139">
         <v>1417.04</v>
@@ -13669,7 +13685,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="140" spans="1:31">
+    <row r="140" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -13764,7 +13780,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="141" spans="1:31">
+    <row r="141" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -13859,7 +13875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="142" spans="1:31">
+    <row r="142" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -13954,7 +13970,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="143" spans="1:31">
+    <row r="143" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -14049,7 +14065,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:31">
+    <row r="144" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -14144,7 +14160,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="145" spans="1:31">
+    <row r="145" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>143</v>
       </c>
@@ -14155,7 +14171,7 @@
         <v>2.44</v>
       </c>
       <c r="D145">
-        <v>86.79000000000001</v>
+        <v>86.79</v>
       </c>
       <c r="E145">
         <v>86.67</v>
@@ -14164,7 +14180,7 @@
         <v>0</v>
       </c>
       <c r="G145">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H145">
         <v>0.71</v>
@@ -14200,7 +14216,7 @@
         <v>2.44</v>
       </c>
       <c r="S145">
-        <v>86.79000000000001</v>
+        <v>86.79</v>
       </c>
       <c r="T145">
         <v>86.67</v>
@@ -14209,7 +14225,7 @@
         <v>0</v>
       </c>
       <c r="V145">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W145">
         <v>0.71</v>
@@ -14239,7 +14255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:31">
+    <row r="146" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -14313,7 +14329,7 @@
         <v>0</v>
       </c>
       <c r="Y146">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="Z146">
         <v>0.52</v>
@@ -14334,7 +14350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:31">
+    <row r="147" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -14429,7 +14445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:31">
+    <row r="148" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>146</v>
       </c>
@@ -14524,7 +14540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:31">
+    <row r="149" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>147</v>
       </c>
@@ -14559,7 +14575,7 @@
         <v>0.15</v>
       </c>
       <c r="L149">
-        <v>533.5599999999999</v>
+        <v>533.55999999999995</v>
       </c>
       <c r="M149">
         <v>661.42</v>
@@ -14601,10 +14617,10 @@
         <v>0.03</v>
       </c>
       <c r="Z149">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA149">
-        <v>533.5599999999999</v>
+        <v>533.55999999999995</v>
       </c>
       <c r="AB149">
         <v>661.42</v>
@@ -14619,7 +14635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:31">
+    <row r="150" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -14642,13 +14658,13 @@
         <v>0.31</v>
       </c>
       <c r="H150">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="I150">
         <v>0</v>
       </c>
       <c r="J150">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K150">
         <v>0.31</v>
@@ -14687,7 +14703,7 @@
         <v>0.31</v>
       </c>
       <c r="W150">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X150">
         <v>0</v>
@@ -14714,7 +14730,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:31">
+    <row r="151" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -14809,7 +14825,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:31">
+    <row r="152" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>150</v>
       </c>
@@ -14883,10 +14899,10 @@
         <v>0</v>
       </c>
       <c r="Y152">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Z152">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA152">
         <v>832.67</v>
@@ -14904,7 +14920,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="153" spans="1:31">
+    <row r="153" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -14942,7 +14958,7 @@
         <v>935.74</v>
       </c>
       <c r="M153">
-        <v>264.9</v>
+        <v>264.89999999999998</v>
       </c>
       <c r="N153" t="s">
         <v>30</v>
@@ -14987,7 +15003,7 @@
         <v>935.74</v>
       </c>
       <c r="AB153">
-        <v>264.9</v>
+        <v>264.89999999999998</v>
       </c>
       <c r="AC153" t="s">
         <v>30</v>
@@ -14999,7 +15015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:31">
+    <row r="154" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -15019,7 +15035,7 @@
         <v>0</v>
       </c>
       <c r="G154">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H154">
         <v>0.71</v>
@@ -15031,7 +15047,7 @@
         <v>0</v>
       </c>
       <c r="K154">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L154">
         <v>1292.79</v>
@@ -15064,7 +15080,7 @@
         <v>0</v>
       </c>
       <c r="V154">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W154">
         <v>0.71</v>
@@ -15094,7 +15110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="155" spans="1:31">
+    <row r="155" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>153</v>
       </c>
@@ -15114,7 +15130,7 @@
         <v>0</v>
       </c>
       <c r="G155">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H155">
         <v>0.71</v>
@@ -15159,7 +15175,7 @@
         <v>0</v>
       </c>
       <c r="V155">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W155">
         <v>0.71</v>
@@ -15189,7 +15205,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="1:31">
+    <row r="156" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -15284,7 +15300,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="157" spans="1:31">
+    <row r="157" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -15295,7 +15311,7 @@
         <v>2.64</v>
       </c>
       <c r="D157">
-        <v>67.76000000000001</v>
+        <v>67.760000000000005</v>
       </c>
       <c r="E157">
         <v>118.18</v>
@@ -15340,7 +15356,7 @@
         <v>2.64</v>
       </c>
       <c r="S157">
-        <v>67.76000000000001</v>
+        <v>67.760000000000005</v>
       </c>
       <c r="T157">
         <v>118.18</v>
@@ -15379,7 +15395,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="158" spans="1:31">
+    <row r="158" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -15390,7 +15406,7 @@
         <v>1.06</v>
       </c>
       <c r="D158">
-        <v>40.16</v>
+        <v>40.159999999999997</v>
       </c>
       <c r="E158">
         <v>95.12</v>
@@ -15435,7 +15451,7 @@
         <v>1.06</v>
       </c>
       <c r="S158">
-        <v>40.16</v>
+        <v>40.159999999999997</v>
       </c>
       <c r="T158">
         <v>95.12</v>
@@ -15474,7 +15490,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="159" spans="1:31">
+    <row r="159" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -15485,7 +15501,7 @@
         <v>1.64</v>
       </c>
       <c r="D159">
-        <v>81.26000000000001</v>
+        <v>81.260000000000005</v>
       </c>
       <c r="E159">
         <v>67.66</v>
@@ -15512,7 +15528,7 @@
         <v>1479.19</v>
       </c>
       <c r="M159">
-        <v>674.3099999999999</v>
+        <v>674.31</v>
       </c>
       <c r="N159" t="s">
         <v>30</v>
@@ -15530,7 +15546,7 @@
         <v>1.64</v>
       </c>
       <c r="S159">
-        <v>81.26000000000001</v>
+        <v>81.260000000000005</v>
       </c>
       <c r="T159">
         <v>67.66</v>
@@ -15557,7 +15573,7 @@
         <v>1479.19</v>
       </c>
       <c r="AB159">
-        <v>674.3099999999999</v>
+        <v>674.31</v>
       </c>
       <c r="AC159" t="s">
         <v>30</v>
@@ -15569,7 +15585,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:31">
+    <row r="160" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -15643,7 +15659,7 @@
         <v>0</v>
       </c>
       <c r="Y160">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="Z160">
         <v>0.52</v>
@@ -15664,7 +15680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:31">
+    <row r="161" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -15699,7 +15715,7 @@
         <v>0.09</v>
       </c>
       <c r="L161">
-        <v>160.8</v>
+        <v>160.80000000000001</v>
       </c>
       <c r="M161">
         <v>483.63</v>
@@ -15744,7 +15760,7 @@
         <v>0.51</v>
       </c>
       <c r="AA161">
-        <v>160.8</v>
+        <v>160.80000000000001</v>
       </c>
       <c r="AB161">
         <v>483.63</v>
@@ -15759,7 +15775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:31">
+    <row r="162" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>160</v>
       </c>
@@ -15773,7 +15789,7 @@
         <v>47.55</v>
       </c>
       <c r="E162">
-        <v>17.26</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -15782,7 +15798,7 @@
         <v>0.31</v>
       </c>
       <c r="H162">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="I162">
         <v>0</v>
@@ -15797,7 +15813,7 @@
         <v>205.29</v>
       </c>
       <c r="M162">
-        <v>913.5700000000001</v>
+        <v>913.57</v>
       </c>
       <c r="N162" t="s">
         <v>30</v>
@@ -15818,7 +15834,7 @@
         <v>47.55</v>
       </c>
       <c r="T162">
-        <v>17.26</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="U162">
         <v>0</v>
@@ -15827,7 +15843,7 @@
         <v>0.31</v>
       </c>
       <c r="W162">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X162">
         <v>0</v>
@@ -15842,7 +15858,7 @@
         <v>205.29</v>
       </c>
       <c r="AB162">
-        <v>913.5700000000001</v>
+        <v>913.57</v>
       </c>
       <c r="AC162" t="s">
         <v>30</v>
@@ -15854,7 +15870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:31">
+    <row r="163" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>161</v>
       </c>
@@ -15949,7 +15965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:31">
+    <row r="164" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>162</v>
       </c>
@@ -15963,7 +15979,7 @@
         <v>62.06</v>
       </c>
       <c r="E164">
-        <v>91.15000000000001</v>
+        <v>91.15</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -16008,7 +16024,7 @@
         <v>62.06</v>
       </c>
       <c r="T164">
-        <v>91.15000000000001</v>
+        <v>91.15</v>
       </c>
       <c r="U164">
         <v>0</v>
@@ -16044,7 +16060,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:31">
+    <row r="165" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>163</v>
       </c>
@@ -16139,7 +16155,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:31">
+    <row r="166" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>164</v>
       </c>
@@ -16234,7 +16250,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:31">
+    <row r="167" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>165</v>
       </c>
@@ -16329,7 +16345,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:31">
+    <row r="168" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A168" s="1">
         <v>166</v>
       </c>
@@ -16337,7 +16353,7 @@
         <v>9351</v>
       </c>
       <c r="C168">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="D168">
         <v>55.11</v>
@@ -16349,7 +16365,7 @@
         <v>0</v>
       </c>
       <c r="G168">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="H168">
         <v>0.31</v>
@@ -16382,7 +16398,7 @@
         <v>9351</v>
       </c>
       <c r="R168">
-        <v>4.23</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="S168">
         <v>55.11</v>
@@ -16394,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="V168">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="W168">
         <v>0.31</v>
@@ -16424,7 +16440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:31">
+    <row r="169" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A169" s="1">
         <v>167</v>
       </c>
@@ -16498,7 +16514,7 @@
         <v>0</v>
       </c>
       <c r="Y169">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="Z169">
         <v>0.43</v>
@@ -16519,7 +16535,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="170" spans="1:31">
+    <row r="170" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A170" s="1">
         <v>168</v>
       </c>
@@ -16530,7 +16546,7 @@
         <v>3</v>
       </c>
       <c r="D170">
-        <v>75.26000000000001</v>
+        <v>75.260000000000005</v>
       </c>
       <c r="E170">
         <v>62.85</v>
@@ -16575,7 +16591,7 @@
         <v>3</v>
       </c>
       <c r="S170">
-        <v>75.26000000000001</v>
+        <v>75.260000000000005</v>
       </c>
       <c r="T170">
         <v>62.85</v>
@@ -16593,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="Y170">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="Z170">
         <v>0.22</v>
@@ -16614,7 +16630,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:31">
+    <row r="171" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A171" s="1">
         <v>169</v>
       </c>
@@ -16625,7 +16641,7 @@
         <v>1.71</v>
       </c>
       <c r="D171">
-        <v>78.84999999999999</v>
+        <v>78.849999999999994</v>
       </c>
       <c r="E171">
         <v>85.16</v>
@@ -16634,7 +16650,7 @@
         <v>0</v>
       </c>
       <c r="G171">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H171">
         <v>0.72</v>
@@ -16670,7 +16686,7 @@
         <v>1.71</v>
       </c>
       <c r="S171">
-        <v>78.84999999999999</v>
+        <v>78.849999999999994</v>
       </c>
       <c r="T171">
         <v>85.16</v>
@@ -16679,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="V171">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="W171">
         <v>0.72</v>
@@ -16709,7 +16725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:31">
+    <row r="172" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -16732,13 +16748,13 @@
         <v>0.42</v>
       </c>
       <c r="H172">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I172">
         <v>0</v>
       </c>
       <c r="J172">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K172">
         <v>0.12</v>
@@ -16777,7 +16793,7 @@
         <v>0.42</v>
       </c>
       <c r="W172">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="X172">
         <v>0</v>
@@ -16786,7 +16802,7 @@
         <v>0.43</v>
       </c>
       <c r="Z172">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA172">
         <v>1156.94</v>
@@ -16804,7 +16820,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="1:31">
+    <row r="173" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -16815,7 +16831,7 @@
         <v>3.32</v>
       </c>
       <c r="D173">
-        <v>68.93000000000001</v>
+        <v>68.930000000000007</v>
       </c>
       <c r="E173">
         <v>49.92</v>
@@ -16860,7 +16876,7 @@
         <v>3.32</v>
       </c>
       <c r="S173">
-        <v>68.93000000000001</v>
+        <v>68.930000000000007</v>
       </c>
       <c r="T173">
         <v>49.92</v>
@@ -16899,7 +16915,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="174" spans="1:31">
+    <row r="174" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -16994,7 +17010,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="175" spans="1:31">
+    <row r="175" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A175" s="1">
         <v>173</v>
       </c>
@@ -17005,10 +17021,10 @@
         <v>2.27</v>
       </c>
       <c r="D175">
-        <v>33.59</v>
+        <v>33.590000000000003</v>
       </c>
       <c r="E175">
-        <v>37.95</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -17050,10 +17066,10 @@
         <v>2.27</v>
       </c>
       <c r="S175">
-        <v>33.59</v>
+        <v>33.590000000000003</v>
       </c>
       <c r="T175">
-        <v>37.95</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="U175">
         <v>0</v>
@@ -17068,7 +17084,7 @@
         <v>0</v>
       </c>
       <c r="Y175">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="Z175">
         <v>0.95</v>
@@ -17089,7 +17105,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:31">
+    <row r="176" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A176" s="1">
         <v>174</v>
       </c>
@@ -17112,7 +17128,7 @@
         <v>0.31</v>
       </c>
       <c r="H176">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -17127,7 +17143,7 @@
         <v>168.22</v>
       </c>
       <c r="M176">
-        <v>137.05</v>
+        <v>137.05000000000001</v>
       </c>
       <c r="N176" t="s">
         <v>30</v>
@@ -17157,7 +17173,7 @@
         <v>0.31</v>
       </c>
       <c r="W176">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X176">
         <v>0</v>
@@ -17172,7 +17188,7 @@
         <v>168.22</v>
       </c>
       <c r="AB176">
-        <v>137.05</v>
+        <v>137.05000000000001</v>
       </c>
       <c r="AC176" t="s">
         <v>30</v>
@@ -17184,7 +17200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:31">
+    <row r="177" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -17279,7 +17295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:31">
+    <row r="178" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A178" s="1">
         <v>176</v>
       </c>
@@ -17308,7 +17324,7 @@
         <v>0</v>
       </c>
       <c r="J178">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K178">
         <v>0.06</v>
@@ -17374,7 +17390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:31">
+    <row r="179" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A179" s="1">
         <v>177</v>
       </c>
@@ -17448,7 +17464,7 @@
         <v>0</v>
       </c>
       <c r="Y179">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="Z179">
         <v>0.42</v>
@@ -17469,7 +17485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:31">
+    <row r="180" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A180" s="1">
         <v>178</v>
       </c>
@@ -17507,7 +17523,7 @@
         <v>501.58</v>
       </c>
       <c r="M180">
-        <v>994.4299999999999</v>
+        <v>994.43</v>
       </c>
       <c r="N180" t="s">
         <v>30</v>
@@ -17543,7 +17559,7 @@
         <v>0</v>
       </c>
       <c r="Y180">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="Z180">
         <v>0.76</v>
@@ -17552,7 +17568,7 @@
         <v>501.58</v>
       </c>
       <c r="AB180">
-        <v>994.4299999999999</v>
+        <v>994.43</v>
       </c>
       <c r="AC180" t="s">
         <v>30</v>
@@ -17564,7 +17580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:31">
+    <row r="181" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A181" s="1">
         <v>179</v>
       </c>
@@ -17593,7 +17609,7 @@
         <v>0</v>
       </c>
       <c r="J181">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K181">
         <v>0</v>
@@ -17659,7 +17675,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:31">
+    <row r="182" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A182" s="1">
         <v>180</v>
       </c>
@@ -17754,7 +17770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="183" spans="1:31">
+    <row r="183" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -17768,7 +17784,7 @@
         <v>63.81</v>
       </c>
       <c r="E183">
-        <v>83.09999999999999</v>
+        <v>83.1</v>
       </c>
       <c r="F183">
         <v>0</v>
@@ -17789,10 +17805,10 @@
         <v>0.12</v>
       </c>
       <c r="L183">
-        <v>809.5599999999999</v>
+        <v>809.56</v>
       </c>
       <c r="M183">
-        <v>619.1900000000001</v>
+        <v>619.19000000000005</v>
       </c>
       <c r="N183" t="s">
         <v>30</v>
@@ -17813,7 +17829,7 @@
         <v>63.81</v>
       </c>
       <c r="T183">
-        <v>83.09999999999999</v>
+        <v>83.1</v>
       </c>
       <c r="U183">
         <v>0</v>
@@ -17834,10 +17850,10 @@
         <v>0.23</v>
       </c>
       <c r="AA183">
-        <v>809.5599999999999</v>
+        <v>809.56</v>
       </c>
       <c r="AB183">
-        <v>619.1900000000001</v>
+        <v>619.19000000000005</v>
       </c>
       <c r="AC183" t="s">
         <v>30</v>
@@ -17849,7 +17865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="184" spans="1:31">
+    <row r="184" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -17860,10 +17876,10 @@
         <v>6.83</v>
       </c>
       <c r="D184">
-        <v>66.26000000000001</v>
+        <v>66.260000000000005</v>
       </c>
       <c r="E184">
-        <v>95.29000000000001</v>
+        <v>95.29</v>
       </c>
       <c r="F184">
         <v>0</v>
@@ -17872,7 +17888,7 @@
         <v>0.43</v>
       </c>
       <c r="H184">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I184">
         <v>0</v>
@@ -17884,10 +17900,10 @@
         <v>0.18</v>
       </c>
       <c r="L184">
-        <v>1076.4</v>
+        <v>1076.4000000000001</v>
       </c>
       <c r="M184">
-        <v>82.73999999999999</v>
+        <v>82.74</v>
       </c>
       <c r="N184" t="s">
         <v>30</v>
@@ -17905,10 +17921,10 @@
         <v>6.83</v>
       </c>
       <c r="S184">
-        <v>66.26000000000001</v>
+        <v>66.260000000000005</v>
       </c>
       <c r="T184">
-        <v>95.29000000000001</v>
+        <v>95.29</v>
       </c>
       <c r="U184">
         <v>0</v>
@@ -17917,7 +17933,7 @@
         <v>0.43</v>
       </c>
       <c r="W184">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="X184">
         <v>0</v>
@@ -17929,10 +17945,10 @@
         <v>0.21</v>
       </c>
       <c r="AA184">
-        <v>1076.4</v>
+        <v>1076.4000000000001</v>
       </c>
       <c r="AB184">
-        <v>82.73999999999999</v>
+        <v>82.74</v>
       </c>
       <c r="AC184" t="s">
         <v>30</v>
@@ -17944,7 +17960,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:31">
+    <row r="185" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -17967,7 +17983,7 @@
         <v>0.19</v>
       </c>
       <c r="H185">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="I185">
         <v>0</v>
@@ -17979,10 +17995,10 @@
         <v>0.04</v>
       </c>
       <c r="L185">
-        <v>788.6799999999999</v>
+        <v>788.68</v>
       </c>
       <c r="M185">
-        <v>935.6900000000001</v>
+        <v>935.69</v>
       </c>
       <c r="N185" t="s">
         <v>30</v>
@@ -18012,7 +18028,7 @@
         <v>0.19</v>
       </c>
       <c r="W185">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="X185">
         <v>0</v>
@@ -18024,10 +18040,10 @@
         <v>0.25</v>
       </c>
       <c r="AA185">
-        <v>788.6799999999999</v>
+        <v>788.68</v>
       </c>
       <c r="AB185">
-        <v>935.6900000000001</v>
+        <v>935.69</v>
       </c>
       <c r="AC185" t="s">
         <v>30</v>
@@ -18039,7 +18055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="186" spans="1:31">
+    <row r="186" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -18134,7 +18150,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="187" spans="1:31">
+    <row r="187" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A187" s="1">
         <v>185</v>
       </c>
@@ -18157,7 +18173,7 @@
         <v>0.31</v>
       </c>
       <c r="H187">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="I187">
         <v>0</v>
@@ -18172,7 +18188,7 @@
         <v>1096.44</v>
       </c>
       <c r="M187">
-        <v>1028.89</v>
+        <v>1028.8900000000001</v>
       </c>
       <c r="N187" t="s">
         <v>30</v>
@@ -18202,7 +18218,7 @@
         <v>0.31</v>
       </c>
       <c r="W187">
-        <v>0.6899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="X187">
         <v>0</v>
@@ -18217,7 +18233,7 @@
         <v>1096.44</v>
       </c>
       <c r="AB187">
-        <v>1028.89</v>
+        <v>1028.8900000000001</v>
       </c>
       <c r="AC187" t="s">
         <v>30</v>
@@ -18229,7 +18245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="1:31">
+    <row r="188" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -18324,7 +18340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="189" spans="1:31">
+    <row r="189" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -18338,7 +18354,7 @@
         <v>76.48</v>
       </c>
       <c r="E189">
-        <v>94.65000000000001</v>
+        <v>94.65</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -18383,7 +18399,7 @@
         <v>76.48</v>
       </c>
       <c r="T189">
-        <v>94.65000000000001</v>
+        <v>94.65</v>
       </c>
       <c r="U189">
         <v>0</v>
@@ -18401,7 +18417,7 @@
         <v>0.18</v>
       </c>
       <c r="Z189">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AA189">
         <v>1348.5</v>
@@ -18419,7 +18435,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="190" spans="1:31">
+    <row r="190" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -18430,10 +18446,10 @@
         <v>1.21</v>
       </c>
       <c r="D190">
-        <v>66.84999999999999</v>
+        <v>66.849999999999994</v>
       </c>
       <c r="E190">
-        <v>79.65000000000001</v>
+        <v>79.650000000000006</v>
       </c>
       <c r="F190">
         <v>0</v>
@@ -18475,10 +18491,10 @@
         <v>1.21</v>
       </c>
       <c r="S190">
-        <v>66.84999999999999</v>
+        <v>66.849999999999994</v>
       </c>
       <c r="T190">
-        <v>79.65000000000001</v>
+        <v>79.650000000000006</v>
       </c>
       <c r="U190">
         <v>0</v>
@@ -18514,7 +18530,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:31">
+    <row r="191" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -18537,7 +18553,7 @@
         <v>0.72</v>
       </c>
       <c r="H191">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="I191">
         <v>0</v>
@@ -18552,7 +18568,7 @@
         <v>1495.39</v>
       </c>
       <c r="M191">
-        <v>37.7</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="N191" t="s">
         <v>30</v>
@@ -18582,7 +18598,7 @@
         <v>0.72</v>
       </c>
       <c r="W191">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="X191">
         <v>0</v>
@@ -18597,7 +18613,7 @@
         <v>1495.39</v>
       </c>
       <c r="AB191">
-        <v>37.7</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="AC191" t="s">
         <v>30</v>
@@ -18609,7 +18625,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="192" spans="1:31">
+    <row r="192" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A192" s="1">
         <v>190</v>
       </c>
@@ -18704,7 +18720,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:31">
+    <row r="193" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -18799,7 +18815,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:31">
+    <row r="194" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A194" s="1">
         <v>192</v>
       </c>
@@ -18894,7 +18910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:31">
+    <row r="195" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -18905,7 +18921,7 @@
         <v>1.57</v>
       </c>
       <c r="D195">
-        <v>87.51000000000001</v>
+        <v>87.51</v>
       </c>
       <c r="E195">
         <v>15.68</v>
@@ -18926,7 +18942,7 @@
         <v>0</v>
       </c>
       <c r="K195">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L195">
         <v>55.13</v>
@@ -18950,7 +18966,7 @@
         <v>1.57</v>
       </c>
       <c r="S195">
-        <v>87.51000000000001</v>
+        <v>87.51</v>
       </c>
       <c r="T195">
         <v>15.68</v>
@@ -18989,7 +19005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:31">
+    <row r="196" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A196" s="1">
         <v>194</v>
       </c>
@@ -19084,7 +19100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:31">
+    <row r="197" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A197" s="1">
         <v>195</v>
       </c>
@@ -19098,7 +19114,7 @@
         <v>47.36</v>
       </c>
       <c r="E197">
-        <v>36.62</v>
+        <v>36.619999999999997</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -19107,7 +19123,7 @@
         <v>0.43</v>
       </c>
       <c r="H197">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I197">
         <v>0</v>
@@ -19122,7 +19138,7 @@
         <v>133.82</v>
       </c>
       <c r="M197">
-        <v>1040.34</v>
+        <v>1040.3399999999999</v>
       </c>
       <c r="N197" t="s">
         <v>30</v>
@@ -19143,7 +19159,7 @@
         <v>47.36</v>
       </c>
       <c r="T197">
-        <v>36.62</v>
+        <v>36.619999999999997</v>
       </c>
       <c r="U197">
         <v>0</v>
@@ -19152,7 +19168,7 @@
         <v>0.43</v>
       </c>
       <c r="W197">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="X197">
         <v>0</v>
@@ -19167,7 +19183,7 @@
         <v>133.82</v>
       </c>
       <c r="AB197">
-        <v>1040.34</v>
+        <v>1040.3399999999999</v>
       </c>
       <c r="AC197" t="s">
         <v>30</v>
@@ -19179,7 +19195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:31">
+    <row r="198" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -19214,10 +19230,10 @@
         <v>0.09</v>
       </c>
       <c r="L198">
-        <v>284.47</v>
+        <v>284.47000000000003</v>
       </c>
       <c r="M198">
-        <v>539.92</v>
+        <v>539.91999999999996</v>
       </c>
       <c r="N198" t="s">
         <v>30</v>
@@ -19259,10 +19275,10 @@
         <v>0.39</v>
       </c>
       <c r="AA198">
-        <v>284.47</v>
+        <v>284.47000000000003</v>
       </c>
       <c r="AB198">
-        <v>539.92</v>
+        <v>539.91999999999996</v>
       </c>
       <c r="AC198" t="s">
         <v>30</v>
@@ -19274,7 +19290,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="199" spans="1:31">
+    <row r="199" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -19288,7 +19304,7 @@
         <v>53.36</v>
       </c>
       <c r="E199">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -19306,10 +19322,10 @@
         <v>0</v>
       </c>
       <c r="K199">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L199">
-        <v>278.29</v>
+        <v>278.29000000000002</v>
       </c>
       <c r="M199">
         <v>904.54</v>
@@ -19333,7 +19349,7 @@
         <v>53.36</v>
       </c>
       <c r="T199">
-        <v>84.59999999999999</v>
+        <v>84.6</v>
       </c>
       <c r="U199">
         <v>0</v>
@@ -19354,7 +19370,7 @@
         <v>0.38</v>
       </c>
       <c r="AA199">
-        <v>278.29</v>
+        <v>278.29000000000002</v>
       </c>
       <c r="AB199">
         <v>904.54</v>
@@ -19369,7 +19385,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="200" spans="1:31">
+    <row r="200" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A200" s="1">
         <v>198</v>
       </c>
@@ -19464,7 +19480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:31">
+    <row r="201" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A201" s="1">
         <v>199</v>
       </c>
@@ -19475,7 +19491,7 @@
         <v>2.74</v>
       </c>
       <c r="D201">
-        <v>89.45999999999999</v>
+        <v>89.46</v>
       </c>
       <c r="E201">
         <v>34.53</v>
@@ -19520,7 +19536,7 @@
         <v>2.74</v>
       </c>
       <c r="S201">
-        <v>89.45999999999999</v>
+        <v>89.46</v>
       </c>
       <c r="T201">
         <v>34.53</v>
@@ -19559,7 +19575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="202" spans="1:31">
+    <row r="202" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -19597,7 +19613,7 @@
         <v>598.16</v>
       </c>
       <c r="M202">
-        <v>935.0599999999999</v>
+        <v>935.06</v>
       </c>
       <c r="N202" t="s">
         <v>30</v>
@@ -19642,7 +19658,7 @@
         <v>598.16</v>
       </c>
       <c r="AB202">
-        <v>935.0599999999999</v>
+        <v>935.06</v>
       </c>
       <c r="AC202" t="s">
         <v>30</v>
@@ -19654,7 +19670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="203" spans="1:31">
+    <row r="203" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A203" s="1">
         <v>201</v>
       </c>
@@ -19665,7 +19681,7 @@
         <v>4.37</v>
       </c>
       <c r="D203">
-        <v>78.15000000000001</v>
+        <v>78.150000000000006</v>
       </c>
       <c r="E203">
         <v>52.28</v>
@@ -19710,7 +19726,7 @@
         <v>4.37</v>
       </c>
       <c r="S203">
-        <v>78.15000000000001</v>
+        <v>78.150000000000006</v>
       </c>
       <c r="T203">
         <v>52.28</v>
@@ -19749,7 +19765,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="204" spans="1:31">
+    <row r="204" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A204" s="1">
         <v>202</v>
       </c>
@@ -19844,7 +19860,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="205" spans="1:31">
+    <row r="205" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A205" s="1">
         <v>203</v>
       </c>
@@ -19858,7 +19874,7 @@
         <v>48.69</v>
       </c>
       <c r="E205">
-        <v>37.77</v>
+        <v>37.770000000000003</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -19903,7 +19919,7 @@
         <v>48.69</v>
       </c>
       <c r="T205">
-        <v>37.77</v>
+        <v>37.770000000000003</v>
       </c>
       <c r="U205">
         <v>0</v>
@@ -19939,7 +19955,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="206" spans="1:31">
+    <row r="206" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A206" s="1">
         <v>204</v>
       </c>
@@ -19950,7 +19966,7 @@
         <v>3.08</v>
       </c>
       <c r="D206">
-        <v>76.70999999999999</v>
+        <v>76.709999999999994</v>
       </c>
       <c r="E206">
         <v>24.26</v>
@@ -19959,7 +19975,7 @@
         <v>0</v>
       </c>
       <c r="G206">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H206">
         <v>0.71</v>
@@ -19995,7 +20011,7 @@
         <v>3.08</v>
       </c>
       <c r="S206">
-        <v>76.70999999999999</v>
+        <v>76.709999999999994</v>
       </c>
       <c r="T206">
         <v>24.26</v>
@@ -20004,7 +20020,7 @@
         <v>0</v>
       </c>
       <c r="V206">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W206">
         <v>0.71</v>
@@ -20034,7 +20050,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="207" spans="1:31">
+    <row r="207" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A207" s="1">
         <v>205</v>
       </c>
@@ -20057,7 +20073,7 @@
         <v>0.19</v>
       </c>
       <c r="H207">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="I207">
         <v>0</v>
@@ -20102,7 +20118,7 @@
         <v>0.19</v>
       </c>
       <c r="W207">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="X207">
         <v>0</v>
@@ -20129,7 +20145,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:31">
+    <row r="208" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A208" s="1">
         <v>206</v>
       </c>
@@ -20152,7 +20168,7 @@
         <v>0.19</v>
       </c>
       <c r="H208">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="I208">
         <v>0</v>
@@ -20197,7 +20213,7 @@
         <v>0.19</v>
       </c>
       <c r="W208">
-        <v>0.8100000000000001</v>
+        <v>0.81</v>
       </c>
       <c r="X208">
         <v>0</v>
@@ -20224,7 +20240,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="209" spans="1:31">
+    <row r="209" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A209" s="1">
         <v>207</v>
       </c>
@@ -20319,7 +20335,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="210" spans="1:31">
+    <row r="210" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A210" s="1">
         <v>208</v>
       </c>
@@ -20414,7 +20430,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:31">
+    <row r="211" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A211" s="1">
         <v>209</v>
       </c>
@@ -20428,7 +20444,7 @@
         <v>25.59</v>
       </c>
       <c r="E211">
-        <v>35.37</v>
+        <v>35.369999999999997</v>
       </c>
       <c r="F211">
         <v>0</v>
@@ -20446,13 +20462,13 @@
         <v>0</v>
       </c>
       <c r="K211">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L211">
         <v>121.78</v>
       </c>
       <c r="M211">
-        <v>66.84999999999999</v>
+        <v>66.849999999999994</v>
       </c>
       <c r="N211" t="s">
         <v>30</v>
@@ -20473,7 +20489,7 @@
         <v>25.59</v>
       </c>
       <c r="T211">
-        <v>35.37</v>
+        <v>35.369999999999997</v>
       </c>
       <c r="U211">
         <v>0</v>
@@ -20488,7 +20504,7 @@
         <v>0</v>
       </c>
       <c r="Y211">
-        <v>0.9399999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="Z211">
         <v>0.79</v>
@@ -20497,7 +20513,7 @@
         <v>121.78</v>
       </c>
       <c r="AB211">
-        <v>66.84999999999999</v>
+        <v>66.849999999999994</v>
       </c>
       <c r="AC211" t="s">
         <v>30</v>
@@ -20509,7 +20525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:31">
+    <row r="212" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A212" s="1">
         <v>210</v>
       </c>
@@ -20544,7 +20560,7 @@
         <v>0.35</v>
       </c>
       <c r="L212">
-        <v>134.98</v>
+        <v>134.97999999999999</v>
       </c>
       <c r="M212">
         <v>192.82</v>
@@ -20589,7 +20605,7 @@
         <v>0.92</v>
       </c>
       <c r="AA212">
-        <v>134.98</v>
+        <v>134.97999999999999</v>
       </c>
       <c r="AB212">
         <v>192.82</v>
@@ -20604,7 +20620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:31">
+    <row r="213" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A213" s="1">
         <v>211</v>
       </c>
@@ -20636,7 +20652,7 @@
         <v>0.23</v>
       </c>
       <c r="K213">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="L213">
         <v>121.94</v>
@@ -20681,7 +20697,7 @@
         <v>0.37</v>
       </c>
       <c r="Z213">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="AA213">
         <v>121.94</v>
@@ -20699,7 +20715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:31">
+    <row r="214" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A214" s="1">
         <v>212</v>
       </c>
@@ -20710,7 +20726,7 @@
         <v>1.24</v>
       </c>
       <c r="D214">
-        <v>74.70999999999999</v>
+        <v>74.709999999999994</v>
       </c>
       <c r="E214">
         <v>94.61</v>
@@ -20728,10 +20744,10 @@
         <v>0</v>
       </c>
       <c r="J214">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="K214">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="L214">
         <v>345.25</v>
@@ -20755,7 +20771,7 @@
         <v>1.24</v>
       </c>
       <c r="S214">
-        <v>74.70999999999999</v>
+        <v>74.709999999999994</v>
       </c>
       <c r="T214">
         <v>94.61</v>
@@ -20773,7 +20789,7 @@
         <v>0</v>
       </c>
       <c r="Y214">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Z214">
         <v>0.3</v>
@@ -20794,7 +20810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:31">
+    <row r="215" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A215" s="1">
         <v>213</v>
       </c>
@@ -20814,7 +20830,7 @@
         <v>0</v>
       </c>
       <c r="G215">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H215">
         <v>0.93</v>
@@ -20859,7 +20875,7 @@
         <v>0</v>
       </c>
       <c r="V215">
-        <v>0.07000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="W215">
         <v>0.93</v>
@@ -20889,7 +20905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:31">
+    <row r="216" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A216" s="1">
         <v>214</v>
       </c>
@@ -20984,7 +21000,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="217" spans="1:31">
+    <row r="217" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A217" s="1">
         <v>215</v>
       </c>
@@ -20998,7 +21014,7 @@
         <v>70.7</v>
       </c>
       <c r="E217">
-        <v>81.09999999999999</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="F217">
         <v>0</v>
@@ -21043,7 +21059,7 @@
         <v>70.7</v>
       </c>
       <c r="T217">
-        <v>81.09999999999999</v>
+        <v>81.099999999999994</v>
       </c>
       <c r="U217">
         <v>0</v>
@@ -21079,7 +21095,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="218" spans="1:31">
+    <row r="218" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A218" s="1">
         <v>216</v>
       </c>
@@ -21090,7 +21106,7 @@
         <v>2.48</v>
       </c>
       <c r="D218">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="E218">
         <v>100.41</v>
@@ -21135,7 +21151,7 @@
         <v>2.48</v>
       </c>
       <c r="S218">
-        <v>70.90000000000001</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="T218">
         <v>100.41</v>
@@ -21174,7 +21190,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="219" spans="1:31">
+    <row r="219" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A219" s="1">
         <v>217</v>
       </c>
@@ -21269,7 +21285,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="220" spans="1:31">
+    <row r="220" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A220" s="1">
         <v>218</v>
       </c>
@@ -21364,7 +21380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="221" spans="1:31">
+    <row r="221" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A221" s="1">
         <v>219</v>
       </c>
@@ -21441,7 +21457,7 @@
         <v>0.1</v>
       </c>
       <c r="Z221">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA221">
         <v>798.62</v>
@@ -21459,7 +21475,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="222" spans="1:31">
+    <row r="222" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A222" s="1">
         <v>220</v>
       </c>
@@ -21467,10 +21483,10 @@
         <v>166350</v>
       </c>
       <c r="C222">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="D222">
-        <v>71.98999999999999</v>
+        <v>71.989999999999995</v>
       </c>
       <c r="E222">
         <v>63.32</v>
@@ -21482,7 +21498,7 @@
         <v>0.42</v>
       </c>
       <c r="H222">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="I222">
         <v>0</v>
@@ -21512,10 +21528,10 @@
         <v>166350</v>
       </c>
       <c r="R222">
-        <v>2.01</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="S222">
-        <v>71.98999999999999</v>
+        <v>71.989999999999995</v>
       </c>
       <c r="T222">
         <v>63.32</v>
@@ -21527,7 +21543,7 @@
         <v>0.42</v>
       </c>
       <c r="W222">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="X222">
         <v>0</v>
@@ -21554,7 +21570,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="223" spans="1:31">
+    <row r="223" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A223" s="1">
         <v>221</v>
       </c>
@@ -21589,7 +21605,7 @@
         <v>0.18</v>
       </c>
       <c r="L223">
-        <v>989.1900000000001</v>
+        <v>989.19</v>
       </c>
       <c r="M223">
         <v>1000.7</v>
@@ -21634,7 +21650,7 @@
         <v>0.41</v>
       </c>
       <c r="AA223">
-        <v>989.1900000000001</v>
+        <v>989.19</v>
       </c>
       <c r="AB223">
         <v>1000.7</v>
@@ -21649,7 +21665,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="224" spans="1:31">
+    <row r="224" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A224" s="1">
         <v>222</v>
       </c>
@@ -21660,7 +21676,7 @@
         <v>2.33</v>
       </c>
       <c r="D224">
-        <v>71.59999999999999</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="E224">
         <v>46.29</v>
@@ -21705,7 +21721,7 @@
         <v>2.33</v>
       </c>
       <c r="S224">
-        <v>71.59999999999999</v>
+        <v>71.599999999999994</v>
       </c>
       <c r="T224">
         <v>46.29</v>
@@ -21744,7 +21760,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="225" spans="1:31">
+    <row r="225" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A225" s="1">
         <v>223</v>
       </c>
@@ -21779,7 +21795,7 @@
         <v>0.12</v>
       </c>
       <c r="L225">
-        <v>1129.89</v>
+        <v>1129.8900000000001</v>
       </c>
       <c r="M225">
         <v>205.69</v>
@@ -21824,7 +21840,7 @@
         <v>0.33</v>
       </c>
       <c r="AA225">
-        <v>1129.89</v>
+        <v>1129.8900000000001</v>
       </c>
       <c r="AB225">
         <v>205.69</v>
@@ -21839,7 +21855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:31">
+    <row r="226" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A226" s="1">
         <v>224</v>
       </c>
@@ -21853,7 +21869,7 @@
         <v>45.32</v>
       </c>
       <c r="E226">
-        <v>38.66</v>
+        <v>38.659999999999997</v>
       </c>
       <c r="F226">
         <v>0</v>
@@ -21898,7 +21914,7 @@
         <v>45.32</v>
       </c>
       <c r="T226">
-        <v>38.66</v>
+        <v>38.659999999999997</v>
       </c>
       <c r="U226">
         <v>0</v>
@@ -21934,7 +21950,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="227" spans="1:31">
+    <row r="227" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A227" s="1">
         <v>225</v>
       </c>
@@ -21945,7 +21961,7 @@
         <v>2.83</v>
       </c>
       <c r="D227">
-        <v>99.06999999999999</v>
+        <v>99.07</v>
       </c>
       <c r="E227">
         <v>73.7</v>
@@ -21969,7 +21985,7 @@
         <v>0.52</v>
       </c>
       <c r="L227">
-        <v>1276.15</v>
+        <v>1276.1500000000001</v>
       </c>
       <c r="M227">
         <v>148.6</v>
@@ -21990,7 +22006,7 @@
         <v>2.83</v>
       </c>
       <c r="S227">
-        <v>99.06999999999999</v>
+        <v>99.07</v>
       </c>
       <c r="T227">
         <v>73.7</v>
@@ -22014,7 +22030,7 @@
         <v>0.7</v>
       </c>
       <c r="AA227">
-        <v>1276.15</v>
+        <v>1276.1500000000001</v>
       </c>
       <c r="AB227">
         <v>148.6</v>
@@ -22029,7 +22045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:31">
+    <row r="228" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A228" s="1">
         <v>226</v>
       </c>
@@ -22037,7 +22053,7 @@
         <v>29901</v>
       </c>
       <c r="C228">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="D228">
         <v>72.75</v>
@@ -22049,7 +22065,7 @@
         <v>0</v>
       </c>
       <c r="G228">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H228">
         <v>0.72</v>
@@ -22067,7 +22083,7 @@
         <v>1418.01</v>
       </c>
       <c r="M228">
-        <v>93.54000000000001</v>
+        <v>93.54</v>
       </c>
       <c r="N228" t="s">
         <v>30</v>
@@ -22082,7 +22098,7 @@
         <v>29901</v>
       </c>
       <c r="R228">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="S228">
         <v>72.75</v>
@@ -22094,7 +22110,7 @@
         <v>0</v>
       </c>
       <c r="V228">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="W228">
         <v>0.72</v>
@@ -22106,13 +22122,13 @@
         <v>0.35</v>
       </c>
       <c r="Z228">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AA228">
         <v>1418.01</v>
       </c>
       <c r="AB228">
-        <v>93.54000000000001</v>
+        <v>93.54</v>
       </c>
       <c r="AC228" t="s">
         <v>30</v>
@@ -22124,7 +22140,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="1:31">
+    <row r="229" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A229" s="1">
         <v>227</v>
       </c>
@@ -22219,7 +22235,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="230" spans="1:31">
+    <row r="230" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A230" s="1">
         <v>228</v>
       </c>
@@ -22314,7 +22330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="1:31">
+    <row r="231" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A231" s="1">
         <v>229</v>
       </c>
@@ -22352,7 +22368,7 @@
         <v>1536.99</v>
       </c>
       <c r="M231">
-        <v>568.1900000000001</v>
+        <v>568.19000000000005</v>
       </c>
       <c r="N231" t="s">
         <v>30</v>
@@ -22397,7 +22413,7 @@
         <v>1536.99</v>
       </c>
       <c r="AB231">
-        <v>568.1900000000001</v>
+        <v>568.19000000000005</v>
       </c>
       <c r="AC231" t="s">
         <v>30</v>
